--- a/outputs/pinnacle_corners_current/pinnacle_corners_26062026.xlsx
+++ b/outputs/pinnacle_corners_current/pinnacle_corners_26062026.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10.05</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>1.51</v>
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10.76</v>
+        <v>10.74</v>
       </c>
       <c r="F3" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="4">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9.050000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>-1.66</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="F11" t="n">
-        <v>3.04</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="12">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.81</v>
+        <v>8.67</v>
       </c>
       <c r="F12" t="n">
-        <v>0.18</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="13">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="19">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.16</v>
+        <v>9.17</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.14</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="20">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.52</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.32</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="21">
@@ -1021,7 +1021,7 @@
         <v>9.67</v>
       </c>
       <c r="F23" t="n">
-        <v>0.41</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="24">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10.59</v>
+        <v>10.57</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.67</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="25">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9.859999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="29">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10.36</v>
+        <v>10.5</v>
       </c>
       <c r="F30" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="31">
@@ -1437,7 +1437,7 @@
         <v>10.83</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.47</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="40">
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>11.16</v>
+        <v>11.13</v>
       </c>
       <c r="F42" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="43">
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10.95</v>
+        <v>10.83</v>
       </c>
       <c r="F43" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>10.5</v>
+        <v>10.49</v>
       </c>
       <c r="F48" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="49">
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10.51</v>
+        <v>10.07</v>
       </c>
       <c r="F50" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="51">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10.55</v>
+        <v>10.11</v>
       </c>
       <c r="F52" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="53">

--- a/outputs/pinnacle_corners_current/pinnacle_corners_26062026.xlsx
+++ b/outputs/pinnacle_corners_current/pinnacle_corners_26062026.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9.949999999999999</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.22</v>
+        <v>10.11</v>
       </c>
       <c r="F4" t="n">
         <v>1.14</v>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9.210000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.66</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="11">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.32</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>3.42</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="12">
@@ -732,10 +732,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.67</v>
+        <v>8.69</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.09</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="13">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8.81</v>
+        <v>8.82</v>
       </c>
       <c r="F15" t="n">
         <v>1.15</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.82</v>
+        <v>7.8</v>
       </c>
       <c r="F16" t="n">
-        <v>0.19</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="17">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10.28</v>
+        <v>10.45</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.11</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="18">
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.17</v>
+        <v>8.74</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.13</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="20">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.210000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="21">
@@ -1000,28 +1000,28 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Finland - Veikkausliiga</t>
+          <t>FIFA - World Cup</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FC Lahti</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9.67</v>
+        <v>9.18</v>
       </c>
       <c r="F23" t="n">
-        <v>0.49</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="24">
@@ -1035,19 +1035,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FC Lahti</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10.57</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.54</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="25">
@@ -1061,19 +1061,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10.15</v>
+        <v>10.59</v>
       </c>
       <c r="F25" t="n">
-        <v>0.35</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="26">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10.26</v>
+        <v>10.15</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.21</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="27">
@@ -1113,19 +1113,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10.06</v>
+        <v>10.26</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="28">
@@ -1139,50 +1139,50 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9.779999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="F28" t="n">
-        <v>1.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Finland - Veikkausliiga</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HJK Klubi 04</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SJK Akatemia</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>9.609999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="F29" t="n">
-        <v>1.44</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1191,19 +1191,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PK-35</t>
+          <t>FC Haka</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mikkelin Palloilijat</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10.5</v>
+        <v>10.24</v>
       </c>
       <c r="F30" t="n">
-        <v>1.98</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="31">
@@ -1217,24 +1217,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FC Haka</t>
+          <t>JIPPO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>EIF</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>10.24</v>
+        <v>9.73</v>
       </c>
       <c r="F31" t="n">
-        <v>0.83</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1243,45 +1243,45 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JIPPO</t>
+          <t>KaPa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EIF</t>
+          <t>JaPS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>9.73</v>
+        <v>10.1</v>
       </c>
       <c r="F32" t="n">
-        <v>1.59</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46201</v>
+        <v>46199</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Finland - Ykkosliiga</t>
+          <t>Iceland - 1. Deild</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KaPa</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JaPS</t>
+          <t>UMF Njardvik</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>10.53</v>
+        <v>11.52</v>
       </c>
       <c r="F33" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="34">
@@ -1295,19 +1295,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Fylkir</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>UMF Njardvik</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>11.52</v>
+        <v>11.83</v>
       </c>
       <c r="F34" t="n">
-        <v>1.13</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="35">
@@ -1321,19 +1321,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fylkir</t>
+          <t>Leiknir Reykjavik</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>IR Reykjavik</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>11.65</v>
+        <v>11.49</v>
       </c>
       <c r="F35" t="n">
-        <v>1.97</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="36">
@@ -1347,24 +1347,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Leiknir Reykjavik</t>
+          <t>UMF Grindavik</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IR Reykjavik</t>
+          <t>Aegir</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>11.49</v>
+        <v>11.63</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.06</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1373,19 +1373,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UMF Grindavik</t>
+          <t>Throttur Reykjavik</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aegir</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>11.63</v>
+        <v>11.36</v>
       </c>
       <c r="F37" t="n">
-        <v>1.94</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="38">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Iceland - 1. Deild</t>
+          <t>Norway - 1st Division</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik</t>
+          <t>Asane Fotball</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11.36</v>
+        <v>10.83</v>
       </c>
       <c r="F38" t="n">
-        <v>2.57</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="39">
@@ -1425,19 +1425,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Asane Fotball</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.46</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1451,19 +1451,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hodd</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>10.53</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="41">
@@ -1477,19 +1477,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Hodd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10.53</v>
+        <v>11.13</v>
       </c>
       <c r="F41" t="n">
-        <v>1.38</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="42">
@@ -1503,19 +1503,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersunds</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>11.13</v>
+        <v>10.83</v>
       </c>
       <c r="F42" t="n">
-        <v>2.01</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1529,19 +1529,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabaek</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Egersunds</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="E43" t="n">
         <v>10.83</v>
       </c>
       <c r="F43" t="n">
-        <v>0.07000000000000001</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="44">
@@ -1555,19 +1555,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stabaek</t>
+          <t>Strommen</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10.83</v>
+        <v>10.63</v>
       </c>
       <c r="F44" t="n">
-        <v>2.15</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="45">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Strommen</t>
+          <t>Stromsgodset</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd BK</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>10.63</v>
+        <v>11.16</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.02</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="46">
@@ -1602,29 +1602,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Norway - 1st Division</t>
+          <t>Sweden - Superettan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Stromsgodset</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Odd BK</t>
+          <t>Orebro SK</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>11.16</v>
+        <v>10.46</v>
       </c>
       <c r="F46" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1633,19 +1633,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Ostersunds FK</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>10.05</v>
+        <v>9.83</v>
       </c>
       <c r="F47" t="n">
-        <v>0.6</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="48">
@@ -1659,24 +1659,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Orebro SK</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>10.49</v>
+        <v>10.07</v>
       </c>
       <c r="F48" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1685,24 +1685,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ostersunds FK</t>
+          <t>Varnamo</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>9.84</v>
+        <v>10.35</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.33</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Norrkoping</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Osters</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>10.07</v>
+        <v>10.11</v>
       </c>
       <c r="F50" t="n">
-        <v>1.71</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="51">
@@ -1737,70 +1737,18 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Varnamo</t>
+          <t>Helsingborgs</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="F51" t="n">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Sweden - Superettan</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Norrkoping</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Norrby</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46201</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Sweden - Superettan</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Sandvikens IF</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Helsingborgs</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F53" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
